--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
